--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260610.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260610.xlsx
@@ -777,369 +777,369 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>6,404,084,696</t>
+          <t>36,000,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.71%</t>
+          <t>3.11%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>36,000,000</t>
+          <t>2,430,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.10%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2,430,000</t>
+          <t>870,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>2.91%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>870,000</t>
+          <t>2,100,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2,100,000</t>
+          <t>1,170,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>1,170,000</t>
+          <t>790,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>790,000</t>
+          <t>830,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>830,000</t>
+          <t>5,492,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>5,492,000</t>
+          <t>1,240,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>1,240,000</t>
+          <t>1,090,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,090,000</t>
+          <t>1,520,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1,520,000</t>
+          <t>16,350,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>16,350,000</t>
+          <t>279,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>279,000</t>
+          <t>840,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>840,000</t>
+          <t>430,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>430,000</t>
+          <t>720,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>720,000</t>
+          <t>1,334,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,110 +1151,110 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,334,000</t>
+          <t>830,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>830,000</t>
+          <t>9,911,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>9,911,000</t>
+          <t>165,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>165,000</t>
+          <t>5,600,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>5,600,000</t>
+          <t>1,497,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
@@ -1283,105 +1283,105 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,497,000</t>
+          <t>570,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>570,000</t>
+          <t>680,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>680,000</t>
+          <t>1,710,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,710,000</t>
+          <t>1,080,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,080,000</t>
+          <t>1,380,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,61 +1393,61 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,380,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,34 +1459,34 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1496,195 +1496,195 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>1,155,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,155,000</t>
+          <t>5,300,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>5,300,000</t>
+          <t>957,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>957,000</t>
+          <t>870,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>870,000</t>
+          <t>1,010,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>1,010,000</t>
+          <t>450,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>78,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>78,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,24 +1701,20 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>6,404,084,696</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -1736,11 +1732,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -1758,11 +1750,7 @@
           <t>-2,240,533,576</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>-1.30%</t>
-        </is>
-      </c>
+      <c r="D73" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
